--- a/caregiver_forms/004_child_care_withdrawal_form--caregiver_forms.xlsx
+++ b/caregiver_forms/004_child_care_withdrawal_form--caregiver_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -781,8 +781,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -810,12 +810,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'moving_out_of_area',_'value':_'moving'}</t>
+          <t>moving_out_of_area</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Moving out of area', 'value': 'moving'}</t>
+          <t>Moving out of area</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'financial_reasons',_'value':_'financial'}</t>
+          <t>financial_reasons</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Financial reasons', 'value': 'financial'}</t>
+          <t>Financial reasons</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfaction_with_service',_'value':_'dissatisfaction'}</t>
+          <t>dissatisfaction_with_service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfaction with service', 'value': 'dissatisfaction'}</t>
+          <t>Dissatisfaction with service</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'transition_to_school',_'value':_'school'}</t>
+          <t>transition_to_school</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Transition to school', 'value': 'school'}</t>
+          <t>Transition to school</t>
         </is>
       </c>
     </row>
@@ -878,12 +878,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
